--- a/Team-Data/2011-12/3-24-2011-12.xlsx
+++ b/Team-Data/2011-12/3-24-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F2" t="n">
         <v>20</v>
       </c>
       <c r="G2" t="n">
-        <v>0.592</v>
+        <v>0.583</v>
       </c>
       <c r="H2" t="n">
         <v>48.8</v>
@@ -679,19 +746,19 @@
         <v>35.8</v>
       </c>
       <c r="J2" t="n">
-        <v>80.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="K2" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L2" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="M2" t="n">
         <v>19.7</v>
       </c>
       <c r="N2" t="n">
-        <v>0.377</v>
+        <v>0.379</v>
       </c>
       <c r="O2" t="n">
         <v>14.8</v>
@@ -700,7 +767,7 @@
         <v>20.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.726</v>
+        <v>0.727</v>
       </c>
       <c r="R2" t="n">
         <v>10.1</v>
@@ -715,13 +782,13 @@
         <v>21.6</v>
       </c>
       <c r="V2" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="X2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y2" t="n">
         <v>5</v>
@@ -739,7 +806,7 @@
         <v>2</v>
       </c>
       <c r="AD2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
@@ -751,7 +818,7 @@
         <v>8</v>
       </c>
       <c r="AH2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
         <v>20</v>
@@ -769,7 +836,7 @@
         <v>14</v>
       </c>
       <c r="AN2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO2" t="n">
         <v>29</v>
@@ -787,22 +854,22 @@
         <v>14</v>
       </c>
       <c r="AT2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU2" t="n">
         <v>10</v>
       </c>
       <c r="AV2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW2" t="n">
         <v>11</v>
       </c>
       <c r="AX2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AZ2" t="n">
         <v>6</v>
@@ -814,7 +881,7 @@
         <v>22</v>
       </c>
       <c r="BC2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-24-2011-12</t>
+          <t>2012-03-24</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>0.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AE3" t="n">
         <v>15</v>
@@ -930,7 +997,7 @@
         <v>12</v>
       </c>
       <c r="AG3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH3" t="n">
         <v>18</v>
@@ -951,10 +1018,10 @@
         <v>23</v>
       </c>
       <c r="AN3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP3" t="n">
         <v>29</v>
@@ -987,7 +1054,7 @@
         <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA3" t="n">
         <v>23</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-24-2011-12</t>
+          <t>2012-03-24</t>
         </is>
       </c>
     </row>
@@ -1025,22 +1092,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E4" t="n">
         <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G4" t="n">
-        <v>0.152</v>
+        <v>0.156</v>
       </c>
       <c r="H4" t="n">
         <v>48.1</v>
       </c>
       <c r="I4" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="J4" t="n">
         <v>80.5</v>
@@ -1049,13 +1116,13 @@
         <v>0.416</v>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="M4" t="n">
         <v>13.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3</v>
+        <v>0.301</v>
       </c>
       <c r="O4" t="n">
         <v>16.4</v>
@@ -1067,31 +1134,31 @@
         <v>0.749</v>
       </c>
       <c r="R4" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S4" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="T4" t="n">
-        <v>39.4</v>
+        <v>39.3</v>
       </c>
       <c r="U4" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V4" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="W4" t="n">
         <v>6.3</v>
       </c>
       <c r="X4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AA4" t="n">
         <v>20</v>
@@ -1103,7 +1170,7 @@
         <v>-13.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE4" t="n">
         <v>30</v>
@@ -1136,19 +1203,19 @@
         <v>30</v>
       </c>
       <c r="AO4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP4" t="n">
         <v>18</v>
       </c>
       <c r="AQ4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR4" t="n">
         <v>24</v>
       </c>
       <c r="AS4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT4" t="n">
         <v>29</v>
@@ -1157,16 +1224,16 @@
         <v>21</v>
       </c>
       <c r="AV4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW4" t="n">
         <v>29</v>
       </c>
       <c r="AX4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ4" t="n">
         <v>9</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-24-2011-12</t>
+          <t>2012-03-24</t>
         </is>
       </c>
     </row>
@@ -1207,37 +1274,37 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E5" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F5" t="n">
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8</v>
+        <v>0.796</v>
       </c>
       <c r="H5" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="I5" t="n">
         <v>37.8</v>
       </c>
       <c r="J5" t="n">
-        <v>82.7</v>
+        <v>82.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0.457</v>
+        <v>0.459</v>
       </c>
       <c r="L5" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="M5" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="N5" t="n">
-        <v>0.374</v>
+        <v>0.381</v>
       </c>
       <c r="O5" t="n">
         <v>15.8</v>
@@ -1246,13 +1313,13 @@
         <v>21.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.727</v>
+        <v>0.729</v>
       </c>
       <c r="R5" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="S5" t="n">
-        <v>32.4</v>
+        <v>32.6</v>
       </c>
       <c r="T5" t="n">
         <v>46.2</v>
@@ -1261,19 +1328,19 @@
         <v>23</v>
       </c>
       <c r="V5" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W5" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X5" t="n">
         <v>5.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="AA5" t="n">
         <v>17.8</v>
@@ -1282,7 +1349,7 @@
         <v>97.59999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="AD5" t="n">
         <v>1</v>
@@ -1297,16 +1364,16 @@
         <v>1</v>
       </c>
       <c r="AH5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI5" t="n">
         <v>5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AK5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL5" t="n">
         <v>18</v>
@@ -1315,22 +1382,22 @@
         <v>19</v>
       </c>
       <c r="AN5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ5" t="n">
         <v>24</v>
       </c>
       <c r="AR5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AT5" t="n">
         <v>1</v>
@@ -1339,19 +1406,19 @@
         <v>4</v>
       </c>
       <c r="AV5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AX5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA5" t="n">
         <v>28</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-24-2011-12</t>
+          <t>2012-03-24</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-4.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AE6" t="n">
         <v>23</v>
@@ -1479,22 +1546,22 @@
         <v>23</v>
       </c>
       <c r="AH6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI6" t="n">
         <v>25</v>
       </c>
       <c r="AJ6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL6" t="n">
         <v>12</v>
       </c>
       <c r="AM6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN6" t="n">
         <v>12</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-24-2011-12</t>
+          <t>2012-03-24</t>
         </is>
       </c>
     </row>
@@ -1571,79 +1638,79 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F7" t="n">
         <v>22</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.551</v>
       </c>
       <c r="H7" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I7" t="n">
         <v>35.9</v>
       </c>
       <c r="J7" t="n">
-        <v>81.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="L7" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="M7" t="n">
         <v>22.6</v>
       </c>
       <c r="N7" t="n">
-        <v>0.333</v>
+        <v>0.335</v>
       </c>
       <c r="O7" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="P7" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.759</v>
+        <v>0.756</v>
       </c>
       <c r="R7" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S7" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="T7" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="U7" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V7" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W7" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="X7" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z7" t="n">
         <v>19.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>95</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC7" t="n">
         <v>1.7</v>
@@ -1658,10 +1725,10 @@
         <v>12</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AI7" t="n">
         <v>19</v>
@@ -1673,7 +1740,7 @@
         <v>20</v>
       </c>
       <c r="AL7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM7" t="n">
         <v>3</v>
@@ -1682,7 +1749,7 @@
         <v>20</v>
       </c>
       <c r="AO7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP7" t="n">
         <v>24</v>
@@ -1691,10 +1758,10 @@
         <v>14</v>
       </c>
       <c r="AR7" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AS7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT7" t="n">
         <v>12</v>
@@ -1709,7 +1776,7 @@
         <v>4</v>
       </c>
       <c r="AX7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AY7" t="n">
         <v>3</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-24-2011-12</t>
+          <t>2012-03-24</t>
         </is>
       </c>
     </row>
@@ -1831,10 +1898,10 @@
         <v>1.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF8" t="n">
         <v>12</v>
@@ -1849,7 +1916,7 @@
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK8" t="n">
         <v>3</v>
@@ -1876,7 +1943,7 @@
         <v>17</v>
       </c>
       <c r="AS8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT8" t="n">
         <v>5</v>
@@ -1891,7 +1958,7 @@
         <v>5</v>
       </c>
       <c r="AX8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY8" t="n">
         <v>30</v>
@@ -1906,7 +1973,7 @@
         <v>1</v>
       </c>
       <c r="BC8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-24-2011-12</t>
+          <t>2012-03-24</t>
         </is>
       </c>
     </row>
@@ -1935,37 +2002,37 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E9" t="n">
         <v>16</v>
       </c>
       <c r="F9" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G9" t="n">
-        <v>0.333</v>
+        <v>0.34</v>
       </c>
       <c r="H9" t="n">
         <v>48.3</v>
       </c>
       <c r="I9" t="n">
-        <v>34.4</v>
+        <v>34.5</v>
       </c>
       <c r="J9" t="n">
-        <v>79</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.435</v>
+        <v>0.436</v>
       </c>
       <c r="L9" t="n">
         <v>4.5</v>
       </c>
       <c r="M9" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="N9" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="O9" t="n">
         <v>16.9</v>
@@ -1974,25 +2041,25 @@
         <v>22.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.762</v>
+        <v>0.761</v>
       </c>
       <c r="R9" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S9" t="n">
-        <v>27.8</v>
+        <v>27.9</v>
       </c>
       <c r="T9" t="n">
-        <v>39.5</v>
+        <v>39.7</v>
       </c>
       <c r="U9" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="V9" t="n">
         <v>15.8</v>
       </c>
       <c r="W9" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X9" t="n">
         <v>3.9</v>
@@ -2007,13 +2074,13 @@
         <v>19.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>90.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>-6.1</v>
+        <v>-5.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AE9" t="n">
         <v>25</v>
@@ -2025,16 +2092,16 @@
         <v>25</v>
       </c>
       <c r="AH9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ9" t="n">
         <v>25</v>
       </c>
       <c r="AK9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL9" t="n">
         <v>26</v>
@@ -2043,7 +2110,7 @@
         <v>27</v>
       </c>
       <c r="AN9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO9" t="n">
         <v>14</v>
@@ -2055,13 +2122,13 @@
         <v>12</v>
       </c>
       <c r="AR9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS9" t="n">
         <v>30</v>
       </c>
       <c r="AT9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU9" t="n">
         <v>26</v>
@@ -2070,7 +2137,7 @@
         <v>27</v>
       </c>
       <c r="AW9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AX9" t="n">
         <v>30</v>
@@ -2082,7 +2149,7 @@
         <v>11</v>
       </c>
       <c r="BA9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB9" t="n">
         <v>28</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-24-2011-12</t>
+          <t>2012-03-24</t>
         </is>
       </c>
     </row>
@@ -2117,70 +2184,70 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
       </c>
       <c r="G10" t="n">
-        <v>0.435</v>
+        <v>0.422</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J10" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="K10" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L10" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M10" t="n">
         <v>21</v>
       </c>
       <c r="N10" t="n">
-        <v>0.387</v>
+        <v>0.388</v>
       </c>
       <c r="O10" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="P10" t="n">
         <v>20</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.768</v>
+        <v>0.766</v>
       </c>
       <c r="R10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="S10" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="T10" t="n">
         <v>39.6</v>
       </c>
       <c r="U10" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="V10" t="n">
         <v>14</v>
       </c>
       <c r="W10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X10" t="n">
         <v>5.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z10" t="n">
         <v>21.8</v>
@@ -2189,25 +2256,25 @@
         <v>17.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>98.09999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.9</v>
+        <v>-2</v>
       </c>
       <c r="AD10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE10" t="n">
         <v>22</v>
       </c>
       <c r="AF10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG10" t="n">
         <v>22</v>
       </c>
       <c r="AH10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI10" t="n">
         <v>10</v>
@@ -2228,7 +2295,7 @@
         <v>2</v>
       </c>
       <c r="AO10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AP10" t="n">
         <v>28</v>
@@ -2240,19 +2307,19 @@
         <v>29</v>
       </c>
       <c r="AS10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AT10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU10" t="n">
         <v>7</v>
       </c>
       <c r="AV10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX10" t="n">
         <v>7</v>
@@ -2261,13 +2328,13 @@
         <v>5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA10" t="n">
         <v>29</v>
       </c>
       <c r="BB10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC10" t="n">
         <v>22</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-24-2011-12</t>
+          <t>2012-03-24</t>
         </is>
       </c>
     </row>
@@ -2299,34 +2366,34 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E11" t="n">
         <v>26</v>
       </c>
       <c r="F11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G11" t="n">
-        <v>0.531</v>
+        <v>0.542</v>
       </c>
       <c r="H11" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I11" t="n">
         <v>37.6</v>
       </c>
       <c r="J11" t="n">
-        <v>83.09999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.452</v>
+        <v>0.454</v>
       </c>
       <c r="L11" t="n">
         <v>7</v>
       </c>
       <c r="M11" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N11" t="n">
         <v>0.36</v>
@@ -2338,34 +2405,34 @@
         <v>20.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.788</v>
+        <v>0.786</v>
       </c>
       <c r="R11" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S11" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T11" t="n">
-        <v>42.1</v>
+        <v>41.9</v>
       </c>
       <c r="U11" t="n">
         <v>20.9</v>
       </c>
       <c r="V11" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="W11" t="n">
         <v>7.3</v>
       </c>
       <c r="X11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA11" t="n">
         <v>18.5</v>
@@ -2374,43 +2441,43 @@
         <v>98.09999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF11" t="n">
         <v>12</v>
       </c>
-      <c r="AF11" t="n">
-        <v>16</v>
-      </c>
       <c r="AG11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI11" t="n">
         <v>7</v>
       </c>
       <c r="AJ11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK11" t="n">
         <v>11</v>
       </c>
       <c r="AL11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN11" t="n">
         <v>10</v>
       </c>
       <c r="AO11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP11" t="n">
         <v>26</v>
@@ -2431,16 +2498,16 @@
         <v>15</v>
       </c>
       <c r="AV11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW11" t="n">
         <v>18</v>
       </c>
       <c r="AX11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AZ11" t="n">
         <v>19</v>
@@ -2449,7 +2516,7 @@
         <v>25</v>
       </c>
       <c r="BB11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC11" t="n">
         <v>16</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-24-2011-12</t>
+          <t>2012-03-24</t>
         </is>
       </c>
     </row>
@@ -2481,46 +2548,46 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F12" t="n">
         <v>19</v>
       </c>
       <c r="G12" t="n">
-        <v>0.596</v>
+        <v>0.587</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>35.1</v>
+        <v>34.9</v>
       </c>
       <c r="J12" t="n">
-        <v>80.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="K12" t="n">
-        <v>0.435</v>
+        <v>0.434</v>
       </c>
       <c r="L12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="M12" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0.367</v>
+        <v>0.363</v>
       </c>
       <c r="O12" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="P12" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.778</v>
+        <v>0.776</v>
       </c>
       <c r="R12" t="n">
         <v>12.3</v>
@@ -2529,13 +2596,13 @@
         <v>31</v>
       </c>
       <c r="T12" t="n">
-        <v>43.4</v>
+        <v>43.2</v>
       </c>
       <c r="U12" t="n">
         <v>18.1</v>
       </c>
       <c r="V12" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W12" t="n">
         <v>8</v>
@@ -2544,7 +2611,7 @@
         <v>5.3</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z12" t="n">
         <v>21.8</v>
@@ -2553,13 +2620,13 @@
         <v>21.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>96.2</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC12" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE12" t="n">
         <v>8</v>
@@ -2571,16 +2638,16 @@
         <v>7</v>
       </c>
       <c r="AH12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ12" t="n">
         <v>20</v>
       </c>
       <c r="AK12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL12" t="n">
         <v>19</v>
@@ -2589,22 +2656,22 @@
         <v>22</v>
       </c>
       <c r="AN12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO12" t="n">
         <v>3</v>
       </c>
       <c r="AP12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR12" t="n">
         <v>8</v>
       </c>
       <c r="AS12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT12" t="n">
         <v>8</v>
@@ -2613,7 +2680,7 @@
         <v>30</v>
       </c>
       <c r="AV12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW12" t="n">
         <v>15</v>
@@ -2622,19 +2689,19 @@
         <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA12" t="n">
         <v>6</v>
       </c>
       <c r="BB12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-24-2011-12</t>
+          <t>2012-03-24</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F13" t="n">
         <v>21</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.553</v>
       </c>
       <c r="H13" t="n">
         <v>48.5</v>
@@ -2681,43 +2748,43 @@
         <v>36.4</v>
       </c>
       <c r="J13" t="n">
-        <v>81.5</v>
+        <v>81.7</v>
       </c>
       <c r="K13" t="n">
-        <v>0.447</v>
+        <v>0.446</v>
       </c>
       <c r="L13" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="M13" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="N13" t="n">
         <v>0.349</v>
       </c>
       <c r="O13" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="P13" t="n">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S13" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T13" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U13" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V13" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="W13" t="n">
         <v>8.1</v>
@@ -2729,43 +2796,43 @@
         <v>4.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AA13" t="n">
         <v>21.6</v>
       </c>
       <c r="AB13" t="n">
-        <v>96.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AD13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF13" t="n">
         <v>10</v>
       </c>
-      <c r="AE13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>9</v>
-      </c>
       <c r="AG13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AH13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI13" t="n">
         <v>14</v>
       </c>
       <c r="AJ13" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AK13" t="n">
         <v>14</v>
       </c>
       <c r="AL13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM13" t="n">
         <v>5</v>
@@ -2774,31 +2841,31 @@
         <v>13</v>
       </c>
       <c r="AO13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AP13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ13" t="n">
         <v>29</v>
       </c>
       <c r="AR13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS13" t="n">
         <v>22</v>
       </c>
       <c r="AT13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AU13" t="n">
         <v>17</v>
       </c>
       <c r="AV13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX13" t="n">
         <v>22</v>
@@ -2807,16 +2874,16 @@
         <v>7</v>
       </c>
       <c r="AZ13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA13" t="n">
         <v>5</v>
       </c>
       <c r="BB13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-24-2011-12</t>
+          <t>2012-03-24</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>2.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE14" t="n">
         <v>6</v>
@@ -2959,13 +3026,13 @@
         <v>9</v>
       </c>
       <c r="AP14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ14" t="n">
         <v>16</v>
       </c>
       <c r="AR14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS14" t="n">
         <v>1</v>
@@ -2977,7 +3044,7 @@
         <v>9</v>
       </c>
       <c r="AV14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW14" t="n">
         <v>30</v>
@@ -2995,10 +3062,10 @@
         <v>11</v>
       </c>
       <c r="BB14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-24-2011-12</t>
+          <t>2012-03-24</t>
         </is>
       </c>
     </row>
@@ -3027,43 +3094,43 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E15" t="n">
         <v>25</v>
       </c>
       <c r="F15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G15" t="n">
-        <v>0.543</v>
+        <v>0.556</v>
       </c>
       <c r="H15" t="n">
         <v>48.4</v>
       </c>
       <c r="I15" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="J15" t="n">
-        <v>82.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L15" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="M15" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0.327</v>
+        <v>0.32</v>
       </c>
       <c r="O15" t="n">
-        <v>17.4</v>
+        <v>17.6</v>
       </c>
       <c r="P15" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="Q15" t="n">
         <v>0.75</v>
@@ -3072,73 +3139,73 @@
         <v>12.1</v>
       </c>
       <c r="S15" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T15" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U15" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V15" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W15" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="X15" t="n">
         <v>5.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA15" t="n">
         <v>20.1</v>
       </c>
-      <c r="AA15" t="n">
-        <v>20</v>
-      </c>
       <c r="AB15" t="n">
-        <v>95.09999999999999</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE15" t="n">
         <v>15</v>
       </c>
       <c r="AF15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AH15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI15" t="n">
         <v>12</v>
       </c>
       <c r="AJ15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AK15" t="n">
         <v>13</v>
       </c>
       <c r="AL15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AN15" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AO15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP15" t="n">
         <v>13</v>
@@ -3150,28 +3217,28 @@
         <v>9</v>
       </c>
       <c r="AS15" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AT15" t="n">
         <v>18</v>
       </c>
       <c r="AU15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW15" t="n">
         <v>1</v>
       </c>
       <c r="AX15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AY15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA15" t="n">
         <v>14</v>
@@ -3180,7 +3247,7 @@
         <v>18</v>
       </c>
       <c r="BC15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-24-2011-12</t>
+          <t>2012-03-24</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="AD16" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3311,7 +3378,7 @@
         <v>1</v>
       </c>
       <c r="AL16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM16" t="n">
         <v>25</v>
@@ -3326,19 +3393,19 @@
         <v>7</v>
       </c>
       <c r="AQ16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT16" t="n">
         <v>15</v>
       </c>
       <c r="AU16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV16" t="n">
         <v>17</v>
@@ -3353,7 +3420,7 @@
         <v>4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA16" t="n">
         <v>7</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-24-2011-12</t>
+          <t>2012-03-24</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E17" t="n">
         <v>22</v>
       </c>
       <c r="F17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G17" t="n">
-        <v>0.458</v>
+        <v>0.468</v>
       </c>
       <c r="H17" t="n">
         <v>48.1</v>
@@ -3409,25 +3476,25 @@
         <v>37.4</v>
       </c>
       <c r="J17" t="n">
-        <v>85.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K17" t="n">
         <v>0.437</v>
       </c>
       <c r="L17" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M17" t="n">
         <v>20</v>
       </c>
       <c r="N17" t="n">
-        <v>0.344</v>
+        <v>0.341</v>
       </c>
       <c r="O17" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="P17" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="Q17" t="n">
         <v>0.79</v>
@@ -3436,16 +3503,16 @@
         <v>12.8</v>
       </c>
       <c r="S17" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="T17" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U17" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="V17" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W17" t="n">
         <v>8.1</v>
@@ -3457,25 +3524,25 @@
         <v>4.9</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>98.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.6</v>
+        <v>-0.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AE17" t="n">
         <v>20</v>
       </c>
       <c r="AF17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
         <v>20</v>
@@ -3499,10 +3566,10 @@
         <v>13</v>
       </c>
       <c r="AN17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO17" t="n">
         <v>16</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>17</v>
       </c>
       <c r="AP17" t="n">
         <v>22</v>
@@ -3514,7 +3581,7 @@
         <v>4</v>
       </c>
       <c r="AS17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT17" t="n">
         <v>19</v>
@@ -3523,10 +3590,10 @@
         <v>3</v>
       </c>
       <c r="AV17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX17" t="n">
         <v>18</v>
@@ -3535,7 +3602,7 @@
         <v>14</v>
       </c>
       <c r="AZ17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA17" t="n">
         <v>18</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-24-2011-12</t>
+          <t>2012-03-24</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3718,13 @@
         <v>-0.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG18" t="n">
         <v>19</v>
@@ -3672,7 +3739,7 @@
         <v>9</v>
       </c>
       <c r="AK18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL18" t="n">
         <v>9</v>
@@ -3687,16 +3754,16 @@
         <v>4</v>
       </c>
       <c r="AP18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AQ18" t="n">
         <v>9</v>
       </c>
       <c r="AR18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT18" t="n">
         <v>3</v>
@@ -3711,10 +3778,10 @@
         <v>22</v>
       </c>
       <c r="AX18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AY18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ18" t="n">
         <v>8</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-24-2011-12</t>
+          <t>2012-03-24</t>
         </is>
       </c>
     </row>
@@ -3755,34 +3822,34 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F19" t="n">
         <v>34</v>
       </c>
       <c r="G19" t="n">
-        <v>0.32</v>
+        <v>0.306</v>
       </c>
       <c r="H19" t="n">
         <v>48.1</v>
       </c>
       <c r="I19" t="n">
-        <v>33.8</v>
+        <v>33.7</v>
       </c>
       <c r="J19" t="n">
-        <v>79.59999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K19" t="n">
         <v>0.424</v>
       </c>
       <c r="L19" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="N19" t="n">
         <v>0.345</v>
@@ -3794,19 +3861,19 @@
         <v>22</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.773</v>
+        <v>0.772</v>
       </c>
       <c r="R19" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="S19" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="T19" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="U19" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="V19" t="n">
         <v>15.3</v>
@@ -3824,19 +3891,19 @@
         <v>19.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>92.7</v>
+        <v>92.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>-6.1</v>
+        <v>-6.5</v>
       </c>
       <c r="AD19" t="n">
         <v>1</v>
       </c>
       <c r="AE19" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AF19" t="n">
         <v>27</v>
@@ -3869,7 +3936,7 @@
         <v>13</v>
       </c>
       <c r="AP19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ19" t="n">
         <v>8</v>
@@ -3893,16 +3960,16 @@
         <v>19</v>
       </c>
       <c r="AX19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY19" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AZ19" t="n">
         <v>14</v>
       </c>
       <c r="BA19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB19" t="n">
         <v>25</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-24-2011-12</t>
+          <t>2012-03-24</t>
         </is>
       </c>
     </row>
@@ -3937,55 +4004,55 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E20" t="n">
         <v>12</v>
       </c>
       <c r="F20" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G20" t="n">
-        <v>0.25</v>
+        <v>0.255</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="J20" t="n">
-        <v>78.59999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="K20" t="n">
         <v>0.445</v>
       </c>
       <c r="L20" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="M20" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="N20" t="n">
-        <v>0.324</v>
+        <v>0.325</v>
       </c>
       <c r="O20" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="P20" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.761</v>
+        <v>0.759</v>
       </c>
       <c r="R20" t="n">
         <v>11.3</v>
       </c>
       <c r="S20" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="T20" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U20" t="n">
         <v>20.9</v>
@@ -3994,7 +4061,7 @@
         <v>15.4</v>
       </c>
       <c r="W20" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X20" t="n">
         <v>4.8</v>
@@ -4006,7 +4073,7 @@
         <v>20.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="AB20" t="n">
         <v>89</v>
@@ -4015,7 +4082,7 @@
         <v>-4.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AE20" t="n">
         <v>28</v>
@@ -4027,10 +4094,10 @@
         <v>28</v>
       </c>
       <c r="AH20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ20" t="n">
         <v>27</v>
@@ -4039,16 +4106,16 @@
         <v>15</v>
       </c>
       <c r="AL20" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM20" t="n">
         <v>29</v>
       </c>
-      <c r="AM20" t="n">
-        <v>30</v>
-      </c>
       <c r="AN20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO20" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AP20" t="n">
         <v>27</v>
@@ -4063,7 +4130,7 @@
         <v>21</v>
       </c>
       <c r="AT20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU20" t="n">
         <v>16</v>
@@ -4072,16 +4139,16 @@
         <v>23</v>
       </c>
       <c r="AW20" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AX20" t="n">
         <v>19</v>
       </c>
       <c r="AY20" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AZ20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA20" t="n">
         <v>27</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-24-2011-12</t>
+          <t>2012-03-24</t>
         </is>
       </c>
     </row>
@@ -4119,28 +4186,28 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F21" t="n">
         <v>25</v>
       </c>
       <c r="G21" t="n">
-        <v>0.49</v>
+        <v>0.479</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="J21" t="n">
-        <v>81.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="K21" t="n">
-        <v>0.438</v>
+        <v>0.437</v>
       </c>
       <c r="L21" t="n">
         <v>7</v>
@@ -4155,28 +4222,28 @@
         <v>19.2</v>
       </c>
       <c r="P21" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.744</v>
+        <v>0.747</v>
       </c>
       <c r="R21" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="S21" t="n">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="T21" t="n">
-        <v>42.3</v>
+        <v>42.1</v>
       </c>
       <c r="U21" t="n">
         <v>20</v>
       </c>
       <c r="V21" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="W21" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="X21" t="n">
         <v>4.4</v>
@@ -4191,16 +4258,16 @@
         <v>22.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>97.3</v>
+        <v>97.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF21" t="n">
         <v>18</v>
@@ -4209,7 +4276,7 @@
         <v>18</v>
       </c>
       <c r="AH21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI21" t="n">
         <v>21</v>
@@ -4218,10 +4285,10 @@
         <v>18</v>
       </c>
       <c r="AK21" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM21" t="n">
         <v>4</v>
@@ -4239,16 +4306,16 @@
         <v>21</v>
       </c>
       <c r="AR21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS21" t="n">
         <v>15</v>
       </c>
       <c r="AT21" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AU21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV21" t="n">
         <v>29</v>
@@ -4257,10 +4324,10 @@
         <v>2</v>
       </c>
       <c r="AX21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ21" t="n">
         <v>24</v>
@@ -4272,7 +4339,7 @@
         <v>12</v>
       </c>
       <c r="BC21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-24-2011-12</t>
+          <t>2012-03-24</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>6.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4391,7 +4458,7 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI22" t="n">
         <v>8</v>
@@ -4448,7 +4515,7 @@
         <v>22</v>
       </c>
       <c r="BA22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-24-2011-12</t>
+          <t>2012-03-24</t>
         </is>
       </c>
     </row>
@@ -4561,10 +4628,10 @@
         <v>2.1</v>
       </c>
       <c r="AD23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE23" t="n">
         <v>4</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>5</v>
       </c>
       <c r="AF23" t="n">
         <v>5</v>
@@ -4594,7 +4661,7 @@
         <v>3</v>
       </c>
       <c r="AO23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP23" t="n">
         <v>11</v>
@@ -4636,7 +4703,7 @@
         <v>24</v>
       </c>
       <c r="BC23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-24-2011-12</t>
+          <t>2012-03-24</t>
         </is>
       </c>
     </row>
@@ -4743,19 +4810,19 @@
         <v>6.6</v>
       </c>
       <c r="AD24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF24" t="n">
         <v>10</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>9</v>
       </c>
       <c r="AG24" t="n">
         <v>9</v>
       </c>
       <c r="AH24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI24" t="n">
         <v>6</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-24-2011-12</t>
+          <t>2012-03-24</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-1</v>
       </c>
       <c r="AD25" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE25" t="n">
         <v>17</v>
@@ -4937,13 +5004,13 @@
         <v>17</v>
       </c>
       <c r="AH25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI25" t="n">
         <v>11</v>
       </c>
       <c r="AJ25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK25" t="n">
         <v>10</v>
@@ -4958,7 +5025,7 @@
         <v>14</v>
       </c>
       <c r="AO25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP25" t="n">
         <v>23</v>
@@ -4970,13 +5037,13 @@
         <v>21</v>
       </c>
       <c r="AS25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT25" t="n">
         <v>20</v>
       </c>
       <c r="AU25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV25" t="n">
         <v>12</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-24-2011-12</t>
+          <t>2012-03-24</t>
         </is>
       </c>
     </row>
@@ -5107,19 +5174,19 @@
         <v>0.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE26" t="n">
         <v>20</v>
       </c>
       <c r="AF26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI26" t="n">
         <v>16</v>
@@ -5140,10 +5207,10 @@
         <v>19</v>
       </c>
       <c r="AO26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ26" t="n">
         <v>2</v>
@@ -5164,13 +5231,13 @@
         <v>13</v>
       </c>
       <c r="AW26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ26" t="n">
         <v>16</v>
@@ -5179,7 +5246,7 @@
         <v>10</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC26" t="n">
         <v>15</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-24-2011-12</t>
+          <t>2012-03-24</t>
         </is>
       </c>
     </row>
@@ -5211,67 +5278,67 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E27" t="n">
         <v>17</v>
       </c>
       <c r="F27" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G27" t="n">
-        <v>0.354</v>
+        <v>0.362</v>
       </c>
       <c r="H27" t="n">
         <v>48.2</v>
       </c>
       <c r="I27" t="n">
-        <v>36.9</v>
+        <v>36.7</v>
       </c>
       <c r="J27" t="n">
-        <v>86.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.428</v>
+        <v>0.426</v>
       </c>
       <c r="L27" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="M27" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0.316</v>
+        <v>0.32</v>
       </c>
       <c r="O27" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="P27" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.75</v>
+        <v>0.749</v>
       </c>
       <c r="R27" t="n">
         <v>13.7</v>
       </c>
       <c r="S27" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="T27" t="n">
-        <v>43.5</v>
+        <v>43.4</v>
       </c>
       <c r="U27" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="V27" t="n">
         <v>14.7</v>
       </c>
       <c r="W27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X27" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y27" t="n">
         <v>6.3</v>
@@ -5280,16 +5347,16 @@
         <v>19.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>97.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC27" t="n">
-        <v>-5.5</v>
+        <v>-5.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AE27" t="n">
         <v>23</v>
@@ -5310,7 +5377,7 @@
         <v>1</v>
       </c>
       <c r="AK27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL27" t="n">
         <v>17</v>
@@ -5319,7 +5386,7 @@
         <v>11</v>
       </c>
       <c r="AN27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO27" t="n">
         <v>10</v>
@@ -5328,13 +5395,13 @@
         <v>12</v>
       </c>
       <c r="AQ27" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AR27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS27" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AT27" t="n">
         <v>7</v>
@@ -5346,7 +5413,7 @@
         <v>14</v>
       </c>
       <c r="AW27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX27" t="n">
         <v>23</v>
@@ -5355,10 +5422,10 @@
         <v>29</v>
       </c>
       <c r="AZ27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-24-2011-12</t>
+          <t>2012-03-24</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E28" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F28" t="n">
         <v>14</v>
       </c>
       <c r="G28" t="n">
-        <v>0.696</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="H28" t="n">
         <v>48.4</v>
@@ -5411,43 +5478,43 @@
         <v>38.6</v>
       </c>
       <c r="J28" t="n">
-        <v>82.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.466</v>
+        <v>0.467</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0.394</v>
+        <v>0.399</v>
       </c>
       <c r="O28" t="n">
         <v>15.6</v>
       </c>
       <c r="P28" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.723</v>
+        <v>0.72</v>
       </c>
       <c r="R28" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S28" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="T28" t="n">
         <v>42.4</v>
       </c>
       <c r="U28" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="V28" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="W28" t="n">
         <v>7</v>
@@ -5459,19 +5526,19 @@
         <v>5</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="AA28" t="n">
         <v>19.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>100.9</v>
+        <v>101.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE28" t="n">
         <v>4</v>
@@ -5483,7 +5550,7 @@
         <v>4</v>
       </c>
       <c r="AH28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI28" t="n">
         <v>1</v>
@@ -5504,40 +5571,40 @@
         <v>1</v>
       </c>
       <c r="AO28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP28" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AQ28" t="n">
         <v>27</v>
       </c>
       <c r="AR28" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AS28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT28" t="n">
         <v>13</v>
       </c>
       <c r="AU28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW28" t="n">
         <v>25</v>
       </c>
       <c r="AX28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY28" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA28" t="n">
         <v>20</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-24-2011-12</t>
+          <t>2012-03-24</t>
         </is>
       </c>
     </row>
@@ -5575,55 +5642,55 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E29" t="n">
         <v>16</v>
       </c>
       <c r="F29" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G29" t="n">
-        <v>0.327</v>
+        <v>0.333</v>
       </c>
       <c r="H29" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I29" t="n">
-        <v>34.5</v>
+        <v>34.4</v>
       </c>
       <c r="J29" t="n">
-        <v>78.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K29" t="n">
         <v>0.44</v>
       </c>
       <c r="L29" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="M29" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="N29" t="n">
-        <v>0.325</v>
+        <v>0.327</v>
       </c>
       <c r="O29" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="P29" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.769</v>
+        <v>0.768</v>
       </c>
       <c r="R29" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="S29" t="n">
-        <v>31.1</v>
+        <v>31</v>
       </c>
       <c r="T29" t="n">
-        <v>41.6</v>
+        <v>41.2</v>
       </c>
       <c r="U29" t="n">
         <v>21.1</v>
@@ -5635,25 +5702,25 @@
         <v>7</v>
       </c>
       <c r="X29" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z29" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="AA29" t="n">
         <v>18.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>91</v>
+        <v>90.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.8</v>
+        <v>-3.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE29" t="n">
         <v>25</v>
@@ -5665,10 +5732,10 @@
         <v>26</v>
       </c>
       <c r="AH29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AI29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ29" t="n">
         <v>28</v>
@@ -5683,37 +5750,37 @@
         <v>20</v>
       </c>
       <c r="AN29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO29" t="n">
         <v>15</v>
       </c>
       <c r="AP29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ29" t="n">
         <v>10</v>
       </c>
       <c r="AR29" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AS29" t="n">
         <v>11</v>
       </c>
       <c r="AT29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV29" t="n">
         <v>22</v>
       </c>
-      <c r="AU29" t="n">
-        <v>14</v>
-      </c>
-      <c r="AV29" t="n">
+      <c r="AW29" t="n">
         <v>24</v>
       </c>
-      <c r="AW29" t="n">
-        <v>26</v>
-      </c>
       <c r="AX29" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY29" t="n">
         <v>12</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-24-2011-12</t>
+          <t>2012-03-24</t>
         </is>
       </c>
     </row>
@@ -5835,10 +5902,10 @@
         <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF30" t="n">
         <v>12</v>
@@ -5856,7 +5923,7 @@
         <v>4</v>
       </c>
       <c r="AK30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL30" t="n">
         <v>30</v>
@@ -5889,7 +5956,7 @@
         <v>11</v>
       </c>
       <c r="AV30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW30" t="n">
         <v>6</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-24-2011-12</t>
+          <t>2012-03-24</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E31" t="n">
         <v>11</v>
       </c>
       <c r="F31" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G31" t="n">
-        <v>0.234</v>
+        <v>0.239</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
@@ -5969,37 +6036,37 @@
         <v>15.9</v>
       </c>
       <c r="N31" t="n">
-        <v>0.319</v>
+        <v>0.321</v>
       </c>
       <c r="O31" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="P31" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.723</v>
+        <v>0.721</v>
       </c>
       <c r="R31" t="n">
         <v>11.8</v>
       </c>
       <c r="S31" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T31" t="n">
         <v>41.6</v>
       </c>
       <c r="U31" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="V31" t="n">
-        <v>15.3</v>
+        <v>15.5</v>
       </c>
       <c r="W31" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X31" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="Y31" t="n">
         <v>4.6</v>
@@ -6014,10 +6081,10 @@
         <v>93.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>-7.3</v>
+        <v>-7.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6035,10 +6102,10 @@
         <v>15</v>
       </c>
       <c r="AJ31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL31" t="n">
         <v>25</v>
@@ -6047,22 +6114,22 @@
         <v>21</v>
       </c>
       <c r="AN31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP31" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AQ31" t="n">
         <v>26</v>
       </c>
       <c r="AR31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS31" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AT31" t="n">
         <v>21</v>
@@ -6071,7 +6138,7 @@
         <v>29</v>
       </c>
       <c r="AV31" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AW31" t="n">
         <v>14</v>
@@ -6080,10 +6147,10 @@
         <v>2</v>
       </c>
       <c r="AY31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA31" t="n">
         <v>24</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-24-2011-12</t>
+          <t>2012-03-24</t>
         </is>
       </c>
     </row>
